--- a/reporting/sample-output/revenue-model.xlsx
+++ b/reporting/sample-output/revenue-model.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Review" sheetId="1" r:id="R9c1ce0e63b734df8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Build" sheetId="2" r:id="R4702de594fe0440e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Inputs" sheetId="3" r:id="R199fbb9b60f34639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Review" sheetId="1" r:id="Rc8c6d6fc0c9a48c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Build" sheetId="2" r:id="R214d1778735a45ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metric Inputs" sheetId="3" r:id="R5862ab0e0c244346"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -241,9 +241,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -293,7 +293,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
